--- a/assets/samples/sample_narrative.xlsx
+++ b/assets/samples/sample_narrative.xlsx
@@ -752,12 +752,13 @@
   <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="4" width="6" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="9" width="11" customWidth="1"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="22" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="17" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1064,7 +1065,7 @@
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="88" customWidth="1"/>
+    <col min="6" max="6" width="60" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">

--- a/assets/samples/sample_narrative.xlsx
+++ b/assets/samples/sample_narrative.xlsx
@@ -6,14 +6,13 @@
   <sheets>
     <sheet sheetId="1" name="x" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="各工程の詳細記述" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="評価結果サマリ" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="68">
   <si>
     <t>No.</t>
   </si>
@@ -217,49 +216,13 @@
   </si>
   <si>
     <t>得意先は商品と請求書を受領し、支払期日までに指定口座へ代金を支払う。入金は入金消込プロセス（別プロセス）で売掛金と照合される。</t>
-  </si>
-  <si>
-    <t>プロセス</t>
-  </si>
-  <si>
-    <t>統制数</t>
-  </si>
-  <si>
-    <t>キー統制</t>
-  </si>
-  <si>
-    <t>整備評価済</t>
-  </si>
-  <si>
-    <t>運用評価済</t>
-  </si>
-  <si>
-    <t>不備件数</t>
-  </si>
-  <si>
-    <t>うち開示すべき重要な不備</t>
-  </si>
-  <si>
-    <t>例外件数</t>
-  </si>
-  <si>
-    <t>販売プロセス（受注〜売上計上）</t>
-  </si>
-  <si>
-    <t>【合計】</t>
-  </si>
-  <si>
-    <t>全社結論</t>
-  </si>
-  <si>
-    <t>財務報告に係る内部統制は有効である（候補）</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -288,25 +251,8 @@
       <sz val="10"/>
       <name val="Yu Gothic"/>
     </font>
-    <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-      <name val="Yu Gothic"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <name val="Yu Gothic"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF157F5B"/>
-      <sz val="10"/>
-      <name val="Yu Gothic"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -321,16 +267,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F6F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF0E7C73"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEAF4F1"/>
       </patternFill>
     </fill>
   </fills>
@@ -376,7 +312,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -393,23 +329,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1272,109 +1191,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="3" width="10" customWidth="1"/>
-    <col min="4" max="5" width="11" customWidth="1"/>
-    <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="B2" s="8">
-        <v>3</v>
-      </c>
-      <c r="C2" s="8">
-        <v>3</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0</v>
-      </c>
-      <c r="E2" s="8">
-        <v>3</v>
-      </c>
-      <c r="F2" s="8">
-        <v>0</v>
-      </c>
-      <c r="G2" s="8">
-        <v>0</v>
-      </c>
-      <c r="H2" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="B3" s="10">
-        <v>3</v>
-      </c>
-      <c r="C3" s="10">
-        <v>3</v>
-      </c>
-      <c r="D3" s="10">
-        <v>0</v>
-      </c>
-      <c r="E3" s="10">
-        <v>3</v>
-      </c>
-      <c r="F3" s="10">
-        <v>0</v>
-      </c>
-      <c r="G3" s="10">
-        <v>0</v>
-      </c>
-      <c r="H3" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
 </file>
--- a/assets/samples/sample_narrative.xlsx
+++ b/assets/samples/sample_narrative.xlsx
@@ -98,7 +98,7 @@
     <t>与信限度内か</t>
   </si>
   <si>
-    <t>R001C001★</t>
+    <t>R001C001*</t>
   </si>
   <si>
     <t>40</t>
@@ -134,7 +134,7 @@
     <t>出荷指図書</t>
   </si>
   <si>
-    <t>R002C002★</t>
+    <t>R002C002*</t>
   </si>
   <si>
     <t>60</t>
@@ -167,7 +167,7 @@
     <t>会計システム</t>
   </si>
   <si>
-    <t>R003C003★</t>
+    <t>R003C003*</t>
   </si>
   <si>
     <t>80</t>
